--- a/EIANN/data/FigT6_mnist_hyperparams_part2.xlsx
+++ b/EIANN/data/FigT6_mnist_hyperparams_part2.xlsx
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wη (H1)</t>
+          <t>η, W (H1)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yη (DendI, H1)</t>
+          <t>η, Y (DendI, H1)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -742,7 +742,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wη (H2)</t>
+          <t>η, W (H2)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -808,7 +808,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Yη (DendI, H2)</t>
+          <t>η, Y (DendI, H2)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -996,7 +996,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wη (Output)</t>
+          <t>η, W (Output)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1106,7 +1106,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Qη (DendI, H1)</t>
+          <t>η, Q (DendI, H1)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rη (DendI, H1)</t>
+          <t>η, R (DendI, H1)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Qη (DendI, H2)</t>
+          <t>η, Q (DendI, H2)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1178,7 +1178,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rη (DendI, H2)</t>
+          <t>η, R (DendI, H2)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QΣ (DendI, H1)</t>
+          <t>Qsum (DendI, H1)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RΣ (DendI, H1)</t>
+          <t>Rsum (DendI, H1)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1254,7 +1254,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QΣ (DendI, H2)</t>
+          <t>Qsum (DendI, H2)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RΣ (DendI, H2)</t>
+          <t>Rsum (DendI, H2)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wτ_θ (H1)</t>
+          <t>τθ, (H1)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1366,7 +1366,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wτ_θ (H2)</t>
+          <t>τθ, (H2)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wτ_θ (Output)</t>
+          <t>τθ, (Output)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
